--- a/install_root/data_demo/SICUE OUT.xlsx
+++ b/install_root/data_demo/SICUE OUT.xlsx
@@ -613,7 +613,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -628,7 +628,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fer.prueba@algo.com</t>
+          <t>rob.prueba@algo.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Laura Prueba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -644,6 +654,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>un_nuevo_plan.html</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
